--- a/data/260731_자금관리_REV03.xlsx
+++ b/data/260731_자금관리_REV03.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\텔스타이엔지\Desktop\500.이창민대표님\관리 대시보드\엑셀데이터 (1)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C60D995C-A986-4A1B-8276-4CF689FD2B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE04A26A-086F-4FF5-84A5-45F54C27C2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-105" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="상세내역" sheetId="3" r:id="rId1"/>
@@ -655,9 +655,6 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -693,6 +690,9 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1001,13 +1001,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
+      <c r="C1" s="29"/>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
       <c r="G1" s="14"/>
       <c r="I1" s="1" t="s">
         <v>21</v>
@@ -1026,11 +1026,11 @@
       </c>
     </row>
     <row r="2" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="14"/>
       <c r="I2" s="12">
         <f>SUMIF(H4:H499,"계약금",G4:G499)</f>
@@ -1093,7 +1093,7 @@
       </c>
     </row>
     <row r="5" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B5" s="18">
+      <c r="B5" s="17">
         <v>2024</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1127,7 +1127,7 @@
       <c r="M5" s="4"/>
     </row>
     <row r="6" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B6" s="19">
+      <c r="B6" s="18">
         <v>2024</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1161,7 +1161,7 @@
       <c r="M6" s="4"/>
     </row>
     <row r="7" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <v>2024</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -1195,7 +1195,7 @@
       <c r="M7" s="6"/>
     </row>
     <row r="8" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B8" s="21">
+      <c r="B8" s="20">
         <v>2024</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -1229,7 +1229,7 @@
       <c r="M8" s="4"/>
     </row>
     <row r="9" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B9" s="19">
+      <c r="B9" s="18">
         <v>2024</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1263,7 +1263,7 @@
       <c r="M9" s="4"/>
     </row>
     <row r="10" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B10" s="20">
+      <c r="B10" s="19">
         <v>2024</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1297,7 +1297,7 @@
       <c r="M10" s="4"/>
     </row>
     <row r="11" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B11" s="21">
+      <c r="B11" s="20">
         <v>2024</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1331,7 +1331,7 @@
       <c r="M11" s="4"/>
     </row>
     <row r="12" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B12" s="19">
+      <c r="B12" s="18">
         <v>2024</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1365,7 +1365,7 @@
       <c r="M12" s="4"/>
     </row>
     <row r="13" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B13" s="19">
+      <c r="B13" s="18">
         <v>2024</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1399,7 +1399,7 @@
       <c r="M13" s="4"/>
     </row>
     <row r="14" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B14" s="20">
+      <c r="B14" s="19">
         <v>2024</v>
       </c>
       <c r="C14" s="1" t="s">
@@ -1433,7 +1433,7 @@
       <c r="M14" s="4"/>
     </row>
     <row r="15" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>2025</v>
       </c>
       <c r="C15" s="1" t="s">
@@ -1467,7 +1467,7 @@
       <c r="M15" s="4"/>
     </row>
     <row r="16" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B16" s="19">
+      <c r="B16" s="18">
         <v>2025</v>
       </c>
       <c r="C16" s="1" t="s">
@@ -1501,7 +1501,7 @@
       <c r="M16" s="4"/>
     </row>
     <row r="17" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B17" s="19">
+      <c r="B17" s="18">
         <v>2025</v>
       </c>
       <c r="C17" s="1" t="s">
@@ -1535,7 +1535,7 @@
       <c r="M17" s="7"/>
     </row>
     <row r="18" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="20">
+      <c r="B18" s="19">
         <v>2025</v>
       </c>
       <c r="C18" s="1" t="s">
@@ -1569,7 +1569,7 @@
       <c r="M18" s="7"/>
     </row>
     <row r="19" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B19" s="22">
+      <c r="B19" s="21">
         <v>2025</v>
       </c>
       <c r="C19" s="1" t="s">
@@ -1603,7 +1603,7 @@
       <c r="M19" s="7"/>
     </row>
     <row r="20" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B20" s="21">
+      <c r="B20" s="20">
         <v>2025</v>
       </c>
       <c r="C20" s="1" t="s">
@@ -1637,7 +1637,7 @@
       <c r="M20" s="7"/>
     </row>
     <row r="21" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B21" s="19">
+      <c r="B21" s="18">
         <v>2025</v>
       </c>
       <c r="C21" s="1" t="s">
@@ -1667,7 +1667,7 @@
       <c r="M21" s="7"/>
     </row>
     <row r="22" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B22" s="19">
+      <c r="B22" s="18">
         <v>2025</v>
       </c>
       <c r="C22" s="1" t="s">
@@ -1697,7 +1697,7 @@
       <c r="M22" s="7"/>
     </row>
     <row r="23" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B23" s="20">
+      <c r="B23" s="19">
         <v>2025</v>
       </c>
       <c r="C23" s="1" t="s">
@@ -1731,7 +1731,7 @@
       <c r="M23" s="7"/>
     </row>
     <row r="24" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B24" s="21">
+      <c r="B24" s="20">
         <v>2025</v>
       </c>
       <c r="C24" s="1" t="s">
@@ -1765,7 +1765,7 @@
       <c r="M24" s="7"/>
     </row>
     <row r="25" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B25" s="19">
+      <c r="B25" s="18">
         <v>2025</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1799,41 +1799,41 @@
       <c r="M25" s="7"/>
     </row>
     <row r="26" spans="2:13" s="8" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B26" s="20">
+      <c r="B26" s="19">
         <v>2025</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="22" t="s">
         <v>58</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="E26" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="F26" s="24" t="s">
+      <c r="E26" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F26" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="24">
         <v>220000000</v>
       </c>
-      <c r="H26" s="25" t="s">
+      <c r="H26" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="24">
         <v>750000</v>
       </c>
-      <c r="J26" s="26"/>
-      <c r="K26" s="25">
+      <c r="J26" s="25"/>
+      <c r="K26" s="24">
         <v>750000</v>
       </c>
-      <c r="L26" s="25">
-        <v>0</v>
-      </c>
-      <c r="M26" s="27"/>
+      <c r="L26" s="24">
+        <v>0</v>
+      </c>
+      <c r="M26" s="26"/>
     </row>
     <row r="27" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>2025</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1867,7 +1867,7 @@
       <c r="M27" s="7"/>
     </row>
     <row r="28" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B28" s="19">
+      <c r="B28" s="18">
         <v>2025</v>
       </c>
       <c r="C28" s="1" t="s">
@@ -1901,7 +1901,7 @@
       <c r="M28" s="7"/>
     </row>
     <row r="29" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B29" s="20">
+      <c r="B29" s="19">
         <v>2025</v>
       </c>
       <c r="C29" s="1" t="s">
@@ -1935,7 +1935,7 @@
       <c r="M29" s="7"/>
     </row>
     <row r="30" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>2025</v>
       </c>
       <c r="C30" s="1" t="s">
@@ -1969,7 +1969,7 @@
       <c r="M30" s="4"/>
     </row>
     <row r="31" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="19">
+      <c r="B31" s="18">
         <v>2025</v>
       </c>
       <c r="C31" s="1" t="s">
@@ -1999,7 +1999,7 @@
       <c r="M31" s="4"/>
     </row>
     <row r="32" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="19">
+      <c r="B32" s="18">
         <v>2025</v>
       </c>
       <c r="C32" s="1" t="s">
@@ -2033,7 +2033,7 @@
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="20">
+      <c r="B33" s="19">
         <v>2025</v>
       </c>
       <c r="C33" s="1" t="s">
@@ -2065,7 +2065,7 @@
       <c r="M33" s="4"/>
     </row>
     <row r="34" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B34" s="22">
+      <c r="B34" s="21">
         <v>2025</v>
       </c>
       <c r="C34" s="1" t="s">
@@ -2099,7 +2099,7 @@
       <c r="M34" s="4"/>
     </row>
     <row r="35" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B35" s="22">
+      <c r="B35" s="21">
         <v>2026</v>
       </c>
       <c r="C35" s="1" t="s">
@@ -2133,7 +2133,7 @@
       <c r="M35" s="4"/>
     </row>
     <row r="36" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="22">
+      <c r="B36" s="21">
         <v>2026</v>
       </c>
       <c r="C36" s="4" t="s">
@@ -2167,7 +2167,7 @@
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="22">
+      <c r="B37" s="21">
         <v>2026</v>
       </c>
       <c r="C37" s="4" t="s">
@@ -2201,7 +2201,7 @@
       <c r="M37" s="4"/>
     </row>
     <row r="38" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B38" s="22">
+      <c r="B38" s="21">
         <v>2026</v>
       </c>
       <c r="C38" s="4" t="s">
@@ -2235,7 +2235,7 @@
       <c r="M38" s="4"/>
     </row>
     <row r="39" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B39" s="21">
+      <c r="B39" s="20">
         <v>2026</v>
       </c>
       <c r="C39" s="4" t="s">
@@ -2269,7 +2269,7 @@
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="19">
+      <c r="B40" s="18">
         <v>2026</v>
       </c>
       <c r="C40" s="4" t="s">
@@ -2303,7 +2303,7 @@
       <c r="M40" s="4"/>
     </row>
     <row r="41" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="20">
+      <c r="B41" s="19">
         <v>2026</v>
       </c>
       <c r="C41" s="4" t="s">
@@ -2335,7 +2335,7 @@
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B42" s="20">
+      <c r="B42" s="19">
         <v>2026</v>
       </c>
       <c r="C42" s="4" t="s">
@@ -2367,7 +2367,7 @@
       <c r="M42" s="4"/>
     </row>
     <row r="43" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="20">
+      <c r="B43" s="19">
         <v>2026</v>
       </c>
       <c r="C43" s="4" t="s">
@@ -2401,7 +2401,7 @@
       <c r="M43" s="4"/>
     </row>
     <row r="44" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B44" s="20">
+      <c r="B44" s="19">
         <v>2026</v>
       </c>
       <c r="C44" s="4" t="s">
@@ -2435,7 +2435,7 @@
       <c r="M44" s="4"/>
     </row>
     <row r="45" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B45" s="20">
+      <c r="B45" s="19">
         <v>2026</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -2469,7 +2469,7 @@
       <c r="M45" s="4"/>
     </row>
     <row r="46" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B46" s="20">
+      <c r="B46" s="19">
         <v>2026</v>
       </c>
       <c r="C46" s="4" t="s">
@@ -2501,7 +2501,7 @@
       <c r="M46" s="4"/>
     </row>
     <row r="47" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B47" s="20">
+      <c r="B47" s="19">
         <v>2026</v>
       </c>
       <c r="C47" s="4" t="s">
@@ -2533,7 +2533,7 @@
       <c r="M47" s="4"/>
     </row>
     <row r="48" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="20">
+      <c r="B48" s="19">
         <v>2026</v>
       </c>
       <c r="C48" s="4" t="s">
@@ -2565,7 +2565,7 @@
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="20">
+      <c r="B49" s="19">
         <v>2026</v>
       </c>
       <c r="C49" s="4" t="s">
@@ -2597,7 +2597,7 @@
       <c r="M49" s="4"/>
     </row>
     <row r="50" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="20">
+      <c r="B50" s="19">
         <v>2026</v>
       </c>
       <c r="C50" s="4" t="s">
@@ -2629,7 +2629,7 @@
       <c r="M50" s="4"/>
     </row>
     <row r="51" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="20">
+      <c r="B51" s="19">
         <v>2026</v>
       </c>
       <c r="C51" s="4" t="s">
@@ -2663,7 +2663,7 @@
       <c r="M51" s="4"/>
     </row>
     <row r="52" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="20">
+      <c r="B52" s="19">
         <v>2026</v>
       </c>
       <c r="C52" s="4" t="s">
@@ -2695,7 +2695,7 @@
       <c r="M52" s="4"/>
     </row>
     <row r="53" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B53" s="20">
+      <c r="B53" s="19">
         <v>2026</v>
       </c>
       <c r="C53" s="4" t="s">
@@ -2727,7 +2727,7 @@
       <c r="M53" s="4"/>
     </row>
     <row r="54" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="20">
+      <c r="B54" s="19">
         <v>2026</v>
       </c>
       <c r="C54" s="4" t="s">
@@ -2761,7 +2761,7 @@
       <c r="M54" s="4"/>
     </row>
     <row r="55" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B55" s="20">
+      <c r="B55" s="19">
         <v>2026</v>
       </c>
       <c r="C55" s="4" t="s">
@@ -2795,7 +2795,7 @@
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B56" s="20">
+      <c r="B56" s="19">
         <v>2026</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -2827,7 +2827,7 @@
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B57" s="20">
+      <c r="B57" s="19">
         <v>2026</v>
       </c>
       <c r="C57" s="4" t="s">
@@ -2859,7 +2859,7 @@
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B58" s="20">
+      <c r="B58" s="19">
         <v>2026</v>
       </c>
       <c r="C58" s="4" t="s">
@@ -2891,7 +2891,7 @@
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B59" s="20">
+      <c r="B59" s="19">
         <v>2026</v>
       </c>
       <c r="C59" s="4" t="s">
@@ -2925,7 +2925,7 @@
       <c r="M59" s="4"/>
     </row>
     <row r="60" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B60" s="20">
+      <c r="B60" s="19">
         <v>2026</v>
       </c>
       <c r="C60" s="4" t="s">
@@ -2959,7 +2959,7 @@
       <c r="M60" s="4"/>
     </row>
     <row r="61" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B61" s="20">
+      <c r="B61" s="19">
         <v>2026</v>
       </c>
       <c r="C61" s="4" t="s">
@@ -2991,7 +2991,7 @@
       <c r="M61" s="4"/>
     </row>
     <row r="62" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B62" s="20">
+      <c r="B62" s="19">
         <v>2026</v>
       </c>
       <c r="C62" s="4" t="s">
@@ -3006,10 +3006,8 @@
       <c r="F62" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G62" s="28">
-        <v>570000000</v>
-      </c>
-      <c r="H62" s="29" t="s">
+      <c r="G62" s="27"/>
+      <c r="H62" s="28" t="s">
         <v>81</v>
       </c>
       <c r="I62" s="5">
@@ -3021,7 +3019,7 @@
       <c r="M62" s="4"/>
     </row>
     <row r="63" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B63" s="20">
+      <c r="B63" s="19">
         <v>2026</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -3036,10 +3034,8 @@
       <c r="F63" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G63" s="28">
-        <v>570000000</v>
-      </c>
-      <c r="H63" s="29" t="s">
+      <c r="G63" s="27"/>
+      <c r="H63" s="28" t="s">
         <v>81</v>
       </c>
       <c r="I63" s="5">
@@ -3051,7 +3047,7 @@
       <c r="M63" s="4"/>
     </row>
     <row r="64" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="20">
+      <c r="B64" s="19">
         <v>2026</v>
       </c>
       <c r="C64" s="4" t="s">
@@ -3066,10 +3062,8 @@
       <c r="F64" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G64" s="28">
-        <v>570000000</v>
-      </c>
-      <c r="H64" s="29" t="s">
+      <c r="G64" s="27"/>
+      <c r="H64" s="28" t="s">
         <v>81</v>
       </c>
       <c r="I64" s="5">
@@ -3081,7 +3075,7 @@
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="20">
+      <c r="B65" s="19">
         <v>2026</v>
       </c>
       <c r="C65" s="4" t="s">
@@ -3115,7 +3109,7 @@
       <c r="M65" s="4"/>
     </row>
     <row r="66" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B66" s="20">
+      <c r="B66" s="19">
         <v>2026</v>
       </c>
       <c r="C66" s="4" t="s">
@@ -3149,7 +3143,7 @@
       <c r="M66" s="4"/>
     </row>
     <row r="67" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B67" s="20">
+      <c r="B67" s="19">
         <v>2026</v>
       </c>
       <c r="C67" s="4" t="s">
@@ -3181,7 +3175,7 @@
       <c r="M67" s="4"/>
     </row>
     <row r="68" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B68" s="20">
+      <c r="B68" s="19">
         <v>2026</v>
       </c>
       <c r="C68" s="4"/>
@@ -3211,7 +3205,7 @@
       <c r="M68" s="4"/>
     </row>
     <row r="69" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B69" s="20">
+      <c r="B69" s="19">
         <v>2026</v>
       </c>
       <c r="C69" s="4"/>
@@ -3239,7 +3233,7 @@
       <c r="M69" s="4"/>
     </row>
     <row r="70" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B70" s="20">
+      <c r="B70" s="19">
         <v>2026</v>
       </c>
       <c r="C70" s="4" t="s">
@@ -3273,7 +3267,7 @@
       <c r="M70" s="4"/>
     </row>
     <row r="71" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B71" s="20">
+      <c r="B71" s="19">
         <v>2026</v>
       </c>
       <c r="C71" s="4" t="s">
@@ -3305,7 +3299,7 @@
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B72" s="20">
+      <c r="B72" s="19">
         <v>2026</v>
       </c>
       <c r="C72" s="4"/>
@@ -3335,7 +3329,7 @@
       <c r="M72" s="4"/>
     </row>
     <row r="73" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B73" s="20">
+      <c r="B73" s="19">
         <v>2026</v>
       </c>
       <c r="C73" s="4"/>
@@ -3365,7 +3359,7 @@
       <c r="M73" s="4"/>
     </row>
     <row r="74" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B74" s="20">
+      <c r="B74" s="19">
         <v>2026</v>
       </c>
       <c r="C74" s="4" t="s">
@@ -3399,7 +3393,7 @@
       <c r="M74" s="4"/>
     </row>
     <row r="75" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B75" s="20">
+      <c r="B75" s="19">
         <v>2026</v>
       </c>
       <c r="C75" s="4"/>
@@ -3429,7 +3423,7 @@
       <c r="M75" s="4"/>
     </row>
     <row r="76" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B76" s="20">
+      <c r="B76" s="19">
         <v>2026</v>
       </c>
       <c r="C76" s="4"/>
@@ -3459,7 +3453,7 @@
       <c r="M76" s="4"/>
     </row>
     <row r="77" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B77" s="20">
+      <c r="B77" s="19">
         <v>2026</v>
       </c>
       <c r="C77" s="4" t="s">
@@ -3491,7 +3485,7 @@
       <c r="M77" s="4"/>
     </row>
     <row r="78" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B78" s="20">
+      <c r="B78" s="19">
         <v>2026</v>
       </c>
       <c r="C78" s="4" t="s">
@@ -3523,7 +3517,7 @@
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B79" s="20">
+      <c r="B79" s="19">
         <v>2026</v>
       </c>
       <c r="C79" s="4" t="s">
@@ -3555,7 +3549,7 @@
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B80" s="20">
+      <c r="B80" s="19">
         <v>2026</v>
       </c>
       <c r="C80" s="4" t="s">
@@ -3587,7 +3581,7 @@
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="2:13" ht="18" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B81" s="20">
+      <c r="B81" s="19">
         <v>2026</v>
       </c>
       <c r="C81" s="4" t="s">
